--- a/spreadsheet_codegen/examples/basic/template_formula.xlsx
+++ b/spreadsheet_codegen/examples/basic/template_formula.xlsx
@@ -633,7 +633,7 @@
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">          excel-codegen render -c &lt;配置&gt;.yaml -x template_formula.xlsx --write-excel</t>
+          <t xml:space="preserve">          spreadsheet-codegen render -c &lt;配置&gt;.yaml -x template_formula.xlsx --write-excel</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">      想确认表里的代码是不是已经过期：excel-codegen check -c &lt;配置&gt;.yaml</t>
+          <t xml:space="preserve">      想确认表里的代码是不是已经过期：spreadsheet-codegen check -c &lt;配置&gt;.yaml</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  命令      excel-codegen render -c examples/example_formula.yaml -x examples/template_formula.xlsx --write-excel --outdir examples/generated_formula</t>
+          <t xml:space="preserve">  命令      spreadsheet-codegen render -c examples/example_formula.yaml -x examples/template_formula.xlsx --write-excel --outdir examples/generated_formula</t>
         </is>
       </c>
     </row>
